--- a/Exc1/Current Architecture Problems.xlsx
+++ b/Exc1/Current Architecture Problems.xlsx
@@ -58,7 +58,7 @@
     <t>Нехватка масштабируемости: с ростом данных и пользователей текущая инфраструктура не выдержит нагрузки</t>
   </si>
   <si>
-    <t>Использование нового DWH + ускорение ETL/ELT-конвейеров</t>
+    <t>Использование нового DWH + ускорение смена шины обмена данными на Kafka. Camel гораздо хуже горизонтально масштабируется + вся логика конвертации между сервисами находится в Camel, что увеличивает их взаимозовисимость. Поэтому Camel нужно заменить</t>
   </si>
   <si>
     <t>Фрагментированность данных: бизнес хочет разделить направления, но в старой системе все завязано на одном хранилище</t>
